--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\github_loxford_pvt\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3104889-176C-4041-A884-114EA3901557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396A4507-CAA8-4DBB-BB26-A015514CBDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="1305" windowWidth="28080" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
   <si>
     <t>Category</t>
   </si>
@@ -370,6 +370,12 @@
   </si>
   <si>
     <t>Model Context Protocol</t>
+  </si>
+  <si>
+    <t>Agents For Management</t>
+  </si>
+  <si>
+    <t>Corporate training</t>
   </si>
 </sst>
 </file>
@@ -711,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="3" customWidth="1"/>
@@ -1251,6 +1257,9 @@
       <c r="D50" t="s">
         <v>47</v>
       </c>
+      <c r="E50" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
@@ -1265,6 +1274,9 @@
       <c r="D51" t="s">
         <v>108</v>
       </c>
+      <c r="E51" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -1308,21 +1320,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" s="3">
-        <v>30</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" t="s">
-        <v>55</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>107</v>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1330,13 +1339,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D57" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1347,24 +1359,24 @@
         <v>25</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="3">
+        <v>25</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" s="3">
-        <v>60</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D60" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1372,13 +1384,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1386,23 +1398,37 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
+        <v>30</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3">
         <v>20</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D63" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D65" t="s">
         <v>92</v>
       </c>
     </row>

--- a/AgenticAI/ROADMAP-AgenticAI.xlsx
+++ b/AgenticAI/ROADMAP-AgenticAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\github_loxford_pvt\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396A4507-CAA8-4DBB-BB26-A015514CBDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473A0682-4723-41B0-8CB8-26FC3207C47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="1305" windowWidth="28080" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="117">
   <si>
     <t>Category</t>
   </si>
@@ -1291,6 +1291,9 @@
       <c r="D52" t="s">
         <v>50</v>
       </c>
+      <c r="E52" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
